--- a/data/trans_orig/P36BPD14_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD14_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces a la semana que consume los vegetales cocinados, la pasta, el arroz u otros platos aderezados con una salsa de tomate, ajo, cebolla o puerro elaborada a fuego lento con aceite de oliva (sofrito) en 2023</t>
+          <t>Población según el número de veces a la semana que consume los vegetales cocinados, la pasta, el arroz u otros platos aderezados con una salsa de tomate, ajo, cebolla o puerro elaborada a fuego lento con aceite de oliva (sofrito) en 2023 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19275</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11654</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29038</t>
+          <t>27433</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19196</t>
+          <t>18514</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39455</t>
+          <t>38827</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22546</t>
+          <t>22087</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39259</t>
+          <t>39673</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44920</t>
+          <t>45075</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70992</t>
+          <t>72094</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>259809</t>
+          <t>259389</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>284168</t>
+          <t>284893</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>243206</t>
+          <t>242717</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>260697</t>
+          <t>260566</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>509953</t>
+          <t>508729</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>540030</t>
+          <t>540373</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,9%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39438</t>
+          <t>39261</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77121</t>
+          <t>78273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64377</t>
+          <t>64177</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92939</t>
+          <t>93526</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>112103</t>
+          <t>111464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>159093</t>
+          <t>158243</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>210482</t>
+          <t>206593</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>268973</t>
+          <t>265516</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>190810</t>
+          <t>189632</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>231372</t>
+          <t>232080</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>413488</t>
+          <t>415220</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>484559</t>
+          <t>485472</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>193508</t>
+          <t>195845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>251467</t>
+          <t>255068</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>208270</t>
+          <t>205703</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>247256</t>
+          <t>249274</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>414424</t>
+          <t>412132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>485568</t>
+          <t>487091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,18%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21499</t>
+          <t>20419</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22043</t>
+          <t>23469</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18605</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36477</t>
+          <t>37720</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98653</t>
+          <t>100639</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133493</t>
+          <t>133516</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85200</t>
+          <t>87014</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114608</t>
+          <t>115678</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>193500</t>
+          <t>194278</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>238770</t>
+          <t>240687</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,7%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164390</t>
+          <t>165446</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200315</t>
+          <t>200019</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>214493</t>
+          <t>213416</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>245205</t>
+          <t>244937</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>389690</t>
+          <t>388163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>435288</t>
+          <t>434930</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,32%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54413</t>
+          <t>52562</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91840</t>
+          <t>92398</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53815</t>
+          <t>52780</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109896</t>
+          <t>112208</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112972</t>
+          <t>114784</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>189351</t>
+          <t>186947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112969</t>
+          <t>111894</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158544</t>
+          <t>156386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123752</t>
+          <t>126019</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>256512</t>
+          <t>257108</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>236675</t>
+          <t>248558</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>387271</t>
+          <t>393212</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,78%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84491</t>
+          <t>83898</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>128312</t>
+          <t>125786</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>118192</t>
+          <t>118919</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>289249</t>
+          <t>288940</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>224411</t>
+          <t>219319</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>430711</t>
+          <t>404853</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>52,28%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>864</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39586</t>
+          <t>39430</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61061</t>
+          <t>61025</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32876</t>
+          <t>32965</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48684</t>
+          <t>50273</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>75655</t>
+          <t>77062</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>103255</t>
+          <t>104162</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116418</t>
+          <t>116752</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>137607</t>
+          <t>137968</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>157832</t>
+          <t>156473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>173671</t>
+          <t>173278</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>280533</t>
+          <t>279734</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>308875</t>
+          <t>307284</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,4%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21877</t>
+          <t>21622</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13496</t>
+          <t>13867</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15884</t>
+          <t>15235</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31564</t>
+          <t>30496</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>145689</t>
+          <t>145673</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>175385</t>
+          <t>175163</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>151278</t>
+          <t>151615</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>175773</t>
+          <t>176105</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>305562</t>
+          <t>306900</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>343175</t>
+          <t>344193</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,35%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>80759</t>
+          <t>80557</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>110377</t>
+          <t>109511</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>73804</t>
+          <t>73035</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>98092</t>
+          <t>95914</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>161630</t>
+          <t>160789</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>198169</t>
+          <t>198064</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,61%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>89282</t>
+          <t>91428</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>141027</t>
+          <t>144813</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>64517</t>
+          <t>57476</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>168504</t>
+          <t>170952</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>137083</t>
+          <t>149029</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>283585</t>
+          <t>286924</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>116595</t>
+          <t>116537</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>163916</t>
+          <t>164421</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>90210</t>
+          <t>85835</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>239758</t>
+          <t>241887</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>192828</t>
+          <t>204201</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>379100</t>
+          <t>378111</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>340105</t>
+          <t>341744</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>402778</t>
+          <t>400275</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>447906</t>
+          <t>442095</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>683705</t>
+          <t>703967</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>821487</t>
+          <t>820741</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1151002</t>
+          <t>1096633</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>74,47%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>24686</t>
+          <t>24326</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23588</t>
+          <t>23774</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>42421</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>234918</t>
+          <t>235243</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>700650</t>
+          <t>703254</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>514098</t>
+          <t>511796</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>553079</t>
+          <t>552177</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>666163</t>
+          <t>632116</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1235196</t>
+          <t>1235445</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,04%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>207836</t>
+          <t>205861</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>686971</t>
+          <t>686424</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>149575</t>
+          <t>149540</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>187181</t>
+          <t>188597</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>377661</t>
+          <t>372809</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>964847</t>
+          <t>992886</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>60,3%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>229983</t>
+          <t>225319</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>336286</t>
+          <t>336566</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,82 +4393,82 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>334765</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>278361</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>375598</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>10,29%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>624924</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>547038</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>692037</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
           <t>9,75%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>334765</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>273694</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>372622</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>624924</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>534808</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>686337</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1093686</t>
+          <t>1105412</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1500316</t>
+          <t>1514335</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1182551</t>
+          <t>1186477</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1570080</t>
+          <t>1581264</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2433520</t>
+          <t>2463622</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3033221</t>
+          <t>3038526</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1636312</t>
+          <t>1625113</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2111407</t>
+          <t>2120096</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1722984</t>
+          <t>1715160</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2193738</t>
+          <t>2185959</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3403865</t>
+          <t>3400038</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4114980</t>
+          <t>4064753</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD14_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD14_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20303</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>13036</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18293</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>12441</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27433</t>
+          <t>27400</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27010</t>
+          <t>31884</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18514</t>
+          <t>22698</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38827</t>
+          <t>41923</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29556</t>
+          <t>37279</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22087</t>
+          <t>28540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39673</t>
+          <t>49132</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>56566</t>
+          <t>69163</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45075</t>
+          <t>55314</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72094</t>
+          <t>84492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>273610</t>
+          <t>275270</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>259389</t>
+          <t>262588</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>284893</t>
+          <t>286134</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>252609</t>
+          <t>271338</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>242717</t>
+          <t>258643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>260566</t>
+          <t>280709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>526218</t>
+          <t>546608</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>508729</t>
+          <t>530756</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>540373</t>
+          <t>562766</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>88,64%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>56236</t>
+          <t>59194</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39261</t>
+          <t>41313</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78273</t>
+          <t>80037</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>77105</t>
+          <t>82167</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64177</t>
+          <t>68162</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93526</t>
+          <t>97584</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>133341</t>
+          <t>141362</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111464</t>
+          <t>118326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158243</t>
+          <t>165514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>238018</t>
+          <t>244525</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>206593</t>
+          <t>214457</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>265516</t>
+          <t>271309</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>211256</t>
+          <t>221572</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>189632</t>
+          <t>201029</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>232080</t>
+          <t>242750</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>449274</t>
+          <t>466097</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>415220</t>
+          <t>430745</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>485472</t>
+          <t>502466</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,69%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>223252</t>
+          <t>226005</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>195845</t>
+          <t>199694</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>255068</t>
+          <t>256684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>226608</t>
+          <t>242755</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>205703</t>
+          <t>221667</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>249274</t>
+          <t>264968</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>449860</t>
+          <t>468760</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>412132</t>
+          <t>431400</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>487091</t>
+          <t>501147</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,57%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>517506</t>
+          <t>529725</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517506</t>
+          <t>529725</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517506</t>
+          <t>529725</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1032475</t>
+          <t>1076219</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1032475</t>
+          <t>1076219</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1032475</t>
+          <t>1076219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20419</t>
+          <t>18684</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>15017</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23469</t>
+          <t>22699</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>26414</t>
+          <t>26131</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18647</t>
+          <t>18379</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37720</t>
+          <t>36128</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>116512</t>
+          <t>113593</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100639</t>
+          <t>95572</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133516</t>
+          <t>130605</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>100251</t>
+          <t>102508</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87014</t>
+          <t>87925</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115678</t>
+          <t>117632</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>216763</t>
+          <t>216102</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>194278</t>
+          <t>194882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>240687</t>
+          <t>239324</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,09%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>182375</t>
+          <t>185904</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>165446</t>
+          <t>168170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200019</t>
+          <t>203437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>230212</t>
+          <t>234911</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>213416</t>
+          <t>218666</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>244937</t>
+          <t>250235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>412586</t>
+          <t>420815</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>388163</t>
+          <t>397488</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>434930</t>
+          <t>443126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,83%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310535</t>
+          <t>310612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310535</t>
+          <t>310612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>310535</t>
+          <t>310612</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>345228</t>
+          <t>352436</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>345228</t>
+          <t>352436</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>345228</t>
+          <t>352436</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>655763</t>
+          <t>663048</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>655763</t>
+          <t>663048</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>655763</t>
+          <t>663048</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>70171</t>
+          <t>92466</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52562</t>
+          <t>69163</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92398</t>
+          <t>114995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>85680</t>
+          <t>99235</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52780</t>
+          <t>83708</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112208</t>
+          <t>116983</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>155851</t>
+          <t>191700</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114784</t>
+          <t>165223</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>186947</t>
+          <t>221591</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>134418</t>
+          <t>148989</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111894</t>
+          <t>124511</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156386</t>
+          <t>175315</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>200986</t>
+          <t>186284</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126019</t>
+          <t>166489</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>257108</t>
+          <t>205003</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>335404</t>
+          <t>335274</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248558</t>
+          <t>303793</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>393212</t>
+          <t>366837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>47,16%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>103043</t>
+          <t>124858</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83898</t>
+          <t>104233</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>125786</t>
+          <t>148863</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>180051</t>
+          <t>126002</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>118919</t>
+          <t>108584</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>288940</t>
+          <t>145934</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>283094</t>
+          <t>250860</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>219319</t>
+          <t>223189</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>404853</t>
+          <t>282116</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>307632</t>
+          <t>366313</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>307632</t>
+          <t>366313</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>307632</t>
+          <t>366313</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>466718</t>
+          <t>411521</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>466718</t>
+          <t>411521</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>466718</t>
+          <t>411521</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>774350</t>
+          <t>777834</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>774350</t>
+          <t>777834</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>774350</t>
+          <t>777834</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>495</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>49295</t>
+          <t>58194</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39430</t>
+          <t>47442</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61025</t>
+          <t>71146</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40278</t>
+          <t>45461</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32965</t>
+          <t>37194</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50273</t>
+          <t>55717</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>89573</t>
+          <t>103654</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>77062</t>
+          <t>89546</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>104162</t>
+          <t>121258</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>128134</t>
+          <t>145577</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116752</t>
+          <t>132536</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>137968</t>
+          <t>156696</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>166069</t>
+          <t>178526</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>156473</t>
+          <t>167791</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>173278</t>
+          <t>186921</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>294203</t>
+          <t>324103</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>279734</t>
+          <t>308091</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>307284</t>
+          <t>339250</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>22350</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>8611</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13867</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>22588</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15235</t>
+          <t>16659</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30496</t>
+          <t>32318</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>160738</t>
+          <t>162124</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>145673</t>
+          <t>149037</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>175163</t>
+          <t>175944</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>163604</t>
+          <t>165107</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>151615</t>
+          <t>151927</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>176105</t>
+          <t>176829</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>324342</t>
+          <t>327231</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>306900</t>
+          <t>309198</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>344193</t>
+          <t>347344</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>64,99%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>93613</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>80557</t>
+          <t>80054</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>109511</t>
+          <t>107157</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>84902</t>
+          <t>90032</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>73035</t>
+          <t>79165</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>95914</t>
+          <t>102959</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>179762</t>
+          <t>183644</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>160789</t>
+          <t>163875</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>198064</t>
+          <t>200674</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>111340</t>
+          <t>122776</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>91428</t>
+          <t>101297</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>144813</t>
+          <t>150322</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>123336</t>
+          <t>146377</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>57476</t>
+          <t>126485</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>170952</t>
+          <t>167817</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>234676</t>
+          <t>269153</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>149029</t>
+          <t>239620</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>286924</t>
+          <t>302246</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>139902</t>
+          <t>162173</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>116537</t>
+          <t>137616</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>164421</t>
+          <t>186169</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>176256</t>
+          <t>217770</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>85835</t>
+          <t>194889</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>241887</t>
+          <t>242947</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>316158</t>
+          <t>379943</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>204201</t>
+          <t>347363</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>378111</t>
+          <t>413742</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>372008</t>
+          <t>433656</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>341744</t>
+          <t>402565</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>400275</t>
+          <t>463939</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>549673</t>
+          <t>407909</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>442095</t>
+          <t>380818</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>703967</t>
+          <t>436690</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>921680</t>
+          <t>841566</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>820741</t>
+          <t>800035</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1096633</t>
+          <t>881917</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>59,16%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>14589</t>
+          <t>17108</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>24326</t>
+          <t>26490</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>15933</t>
+          <t>18657</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>11605</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23774</t>
+          <t>27871</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>30522</t>
+          <t>35765</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>25911</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>49158</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>510181</t>
+          <t>596521</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>235243</t>
+          <t>568731</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>703254</t>
+          <t>621869</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>532644</t>
+          <t>612259</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>511796</t>
+          <t>589328</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>552177</t>
+          <t>636308</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1042826</t>
+          <t>1208779</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>632116</t>
+          <t>1169306</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1235445</t>
+          <t>1241194</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>76,17%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>403950</t>
+          <t>184444</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>205861</t>
+          <t>158507</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>686424</t>
+          <t>209977</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>169154</t>
+          <t>200416</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>149540</t>
+          <t>178262</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>188597</t>
+          <t>223670</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>573104</t>
+          <t>384859</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>372809</t>
+          <t>353268</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>992886</t>
+          <t>422257</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,32 +4373,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>290159</t>
+          <t>331214</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>225319</t>
+          <t>293997</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>336566</t>
+          <t>378638</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,32 +4408,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>334765</t>
+          <t>380343</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>278361</t>
+          <t>348575</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>375598</t>
+          <t>416155</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>624924</t>
+          <t>711557</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>547038</t>
+          <t>659977</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>692037</t>
+          <t>767367</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -4486,32 +4486,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1376073</t>
+          <t>1518003</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1105412</t>
+          <t>1457276</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1514335</t>
+          <t>1581529</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1454832</t>
+          <t>1588242</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1186477</t>
+          <t>1536739</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1581264</t>
+          <t>1642008</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2830905</t>
+          <t>3106244</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2463622</t>
+          <t>3025277</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3038526</t>
+          <t>3194034</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -4599,32 +4599,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1781231</t>
+          <t>1669328</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1625113</t>
+          <t>1600993</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2120096</t>
+          <t>1730392</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,32 +4634,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1859278</t>
+          <t>1751889</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1715160</t>
+          <t>1699075</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2185959</t>
+          <t>1808235</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>3640508</t>
+          <t>3421217</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3400038</t>
+          <t>3334668</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4064753</t>
+          <t>3499752</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3447463</t>
+          <t>3518545</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3447463</t>
+          <t>3518545</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3447463</t>
+          <t>3518545</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3648875</t>
+          <t>3720474</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3648875</t>
+          <t>3720474</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3648875</t>
+          <t>3720474</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7096338</t>
+          <t>7239019</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7096338</t>
+          <t>7239019</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7096338</t>
+          <t>7239019</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
